--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2304"/>
+  <dimension ref="A1:C2318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34990,6 +34990,216 @@
         <v>0.049653</v>
       </c>
     </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2305" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2305" t="n">
+        <v>0.044772</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2306" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2306" t="n">
+        <v>0.04655</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2307" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2307" t="n">
+        <v>0.047059</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2308" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2308" t="n">
+        <v>0.047404</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2309" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2309" t="n">
+        <v>0.048719</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2310" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2310" t="n">
+        <v>0.050417</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2311" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2311" t="n">
+        <v>0.049654</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2312" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2312" t="n">
+        <v>0.044953</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2313" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2313" t="n">
+        <v>0.04660599999999999</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2314" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2314" t="n">
+        <v>0.047066</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2315" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2315" t="n">
+        <v>0.04731900000000001</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2316" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2316" t="n">
+        <v>0.048515</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2317" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2317" t="n">
+        <v>0.050173</v>
+      </c>
+    </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B2318" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2318" t="n">
+        <v>0.049401</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2318"/>
+  <dimension ref="A1:C2339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35200,6 +35200,321 @@
         <v>0.049401</v>
       </c>
     </row>
+    <row r="2319">
+      <c r="A2319" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2319" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2319" t="n">
+        <v>0.045269</v>
+      </c>
+    </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2320" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2320" t="n">
+        <v>0.046685</v>
+      </c>
+    </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2321" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2321" t="n">
+        <v>0.04703599999999999</v>
+      </c>
+    </row>
+    <row r="2322">
+      <c r="A2322" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2322" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2322" t="n">
+        <v>0.047227</v>
+      </c>
+    </row>
+    <row r="2323">
+      <c r="A2323" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2323" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2323" t="n">
+        <v>0.048319</v>
+      </c>
+    </row>
+    <row r="2324">
+      <c r="A2324" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2324" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2324" t="n">
+        <v>0.04995</v>
+      </c>
+    </row>
+    <row r="2325">
+      <c r="A2325" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2325" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2325" t="n">
+        <v>0.04917</v>
+      </c>
+    </row>
+    <row r="2326">
+      <c r="A2326" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2326" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2326" t="n">
+        <v>0.04494</v>
+      </c>
+    </row>
+    <row r="2327">
+      <c r="A2327" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2327" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2327" t="n">
+        <v>0.04616</v>
+      </c>
+    </row>
+    <row r="2328">
+      <c r="A2328" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2328" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2328" t="n">
+        <v>0.046338</v>
+      </c>
+    </row>
+    <row r="2329">
+      <c r="A2329" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2329" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2329" t="n">
+        <v>0.04633</v>
+      </c>
+    </row>
+    <row r="2330">
+      <c r="A2330" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2330" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2330" t="n">
+        <v>0.047345</v>
+      </c>
+    </row>
+    <row r="2331">
+      <c r="A2331" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2331" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2331" t="n">
+        <v>0.04904</v>
+      </c>
+    </row>
+    <row r="2332">
+      <c r="A2332" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2332" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2332" t="n">
+        <v>0.048295</v>
+      </c>
+    </row>
+    <row r="2333">
+      <c r="A2333" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2333" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2333" t="n">
+        <v>0.044674</v>
+      </c>
+    </row>
+    <row r="2334">
+      <c r="A2334" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2334" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2334" t="n">
+        <v>0.045937</v>
+      </c>
+    </row>
+    <row r="2335">
+      <c r="A2335" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2335" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2335" t="n">
+        <v>0.046185</v>
+      </c>
+    </row>
+    <row r="2336">
+      <c r="A2336" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2336" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2336" t="n">
+        <v>0.046221</v>
+      </c>
+    </row>
+    <row r="2337">
+      <c r="A2337" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2337" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2337" t="n">
+        <v>0.04727000000000001</v>
+      </c>
+    </row>
+    <row r="2338">
+      <c r="A2338" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2338" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2338" t="n">
+        <v>0.049005</v>
+      </c>
+    </row>
+    <row r="2339">
+      <c r="A2339" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B2339" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2339" t="n">
+        <v>0.048272</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2339"/>
+  <dimension ref="A1:C2353"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35515,6 +35515,216 @@
         <v>0.048272</v>
       </c>
     </row>
+    <row r="2340">
+      <c r="A2340" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2340" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2340" t="n">
+        <v>0.044984</v>
+      </c>
+    </row>
+    <row r="2341">
+      <c r="A2341" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2341" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2341" t="n">
+        <v>0.046239</v>
+      </c>
+    </row>
+    <row r="2342">
+      <c r="A2342" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2342" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2342" t="n">
+        <v>0.046454</v>
+      </c>
+    </row>
+    <row r="2343">
+      <c r="A2343" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2343" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2343" t="n">
+        <v>0.04656</v>
+      </c>
+    </row>
+    <row r="2344">
+      <c r="A2344" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2344" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2344" t="n">
+        <v>0.047665</v>
+      </c>
+    </row>
+    <row r="2345">
+      <c r="A2345" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2345" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2345" t="n">
+        <v>0.049425</v>
+      </c>
+    </row>
+    <row r="2346">
+      <c r="A2346" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2346" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2346" t="n">
+        <v>0.048682</v>
+      </c>
+    </row>
+    <row r="2347">
+      <c r="A2347" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2347" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2347" t="n">
+        <v>0.045074</v>
+      </c>
+    </row>
+    <row r="2348">
+      <c r="A2348" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2348" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2348" t="n">
+        <v>0.046445</v>
+      </c>
+    </row>
+    <row r="2349">
+      <c r="A2349" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2349" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2349" t="n">
+        <v>0.04663999999999999</v>
+      </c>
+    </row>
+    <row r="2350">
+      <c r="A2350" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2350" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2350" t="n">
+        <v>0.046643</v>
+      </c>
+    </row>
+    <row r="2351">
+      <c r="A2351" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2351" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2351" t="n">
+        <v>0.047569</v>
+      </c>
+    </row>
+    <row r="2352">
+      <c r="A2352" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2352" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2352" t="n">
+        <v>0.049133</v>
+      </c>
+    </row>
+    <row r="2353">
+      <c r="A2353" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2353" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2353" t="n">
+        <v>0.04831000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2353"/>
+  <dimension ref="A1:C2374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35725,6 +35725,321 @@
         <v>0.04831000000000001</v>
       </c>
     </row>
+    <row r="2354">
+      <c r="A2354" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2354" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2354" t="n">
+        <v>0.045363</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2355" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2355" t="n">
+        <v>0.046809</v>
+      </c>
+    </row>
+    <row r="2356">
+      <c r="A2356" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2356" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2356" t="n">
+        <v>0.047009</v>
+      </c>
+    </row>
+    <row r="2357">
+      <c r="A2357" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2357" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2357" t="n">
+        <v>0.04695000000000001</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2358" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2358" t="n">
+        <v>0.047815</v>
+      </c>
+    </row>
+    <row r="2359">
+      <c r="A2359" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2359" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2359" t="n">
+        <v>0.049242</v>
+      </c>
+    </row>
+    <row r="2360">
+      <c r="A2360" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2360" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2360" t="n">
+        <v>0.04837900000000001</v>
+      </c>
+    </row>
+    <row r="2361">
+      <c r="A2361" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2361" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2361" t="n">
+        <v>0.043883</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2362" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2362" t="n">
+        <v>0.044908</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2363" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2363" t="n">
+        <v>0.044969</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2364" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2364" t="n">
+        <v>0.044895</v>
+      </c>
+    </row>
+    <row r="2365">
+      <c r="A2365" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2365" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2365" t="n">
+        <v>0.04585</v>
+      </c>
+    </row>
+    <row r="2366">
+      <c r="A2366" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2366" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2366" t="n">
+        <v>0.0475</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B2367" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2367" t="n">
+        <v>0.046775</v>
+      </c>
+    </row>
+    <row r="2368">
+      <c r="A2368" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2368" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2368" t="n">
+        <v>0.04423</v>
+      </c>
+    </row>
+    <row r="2369">
+      <c r="A2369" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2369" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2369" t="n">
+        <v>0.04532199999999999</v>
+      </c>
+    </row>
+    <row r="2370">
+      <c r="A2370" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2370" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2370" t="n">
+        <v>0.045386</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2371" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2371" t="n">
+        <v>0.045281</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2372" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2372" t="n">
+        <v>0.046203</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2373" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2373" t="n">
+        <v>0.047815</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2374" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2374" t="n">
+        <v>0.047065</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2374"/>
+  <dimension ref="A1:C2388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36040,6 +36040,216 @@
         <v>0.047065</v>
       </c>
     </row>
+    <row r="2375">
+      <c r="A2375" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2375" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2375" t="n">
+        <v>0.044585</v>
+      </c>
+    </row>
+    <row r="2376">
+      <c r="A2376" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2376" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2376" t="n">
+        <v>0.045614</v>
+      </c>
+    </row>
+    <row r="2377">
+      <c r="A2377" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2377" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2377" t="n">
+        <v>0.04561</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2378" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2378" t="n">
+        <v>0.04542500000000001</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2379" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2379" t="n">
+        <v>0.046145</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2380" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2380" t="n">
+        <v>0.04764</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2381" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2381" t="n">
+        <v>0.04683200000000001</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2382" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2382" t="n">
+        <v>0.04481499999999999</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2383" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2383" t="n">
+        <v>0.04590200000000001</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2384" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2384" t="n">
+        <v>0.045876</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2385" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2385" t="n">
+        <v>0.045586</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2386" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2386" t="n">
+        <v>0.04622899999999999</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2387" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2387" t="n">
+        <v>0.047676</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2388" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2388" t="n">
+        <v>0.046868</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_raw/SOFR_OIS_latest.xlsx
+++ b/data_raw/SOFR_OIS_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2388"/>
+  <dimension ref="A1:C2409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36250,6 +36250,321 @@
         <v>0.046868</v>
       </c>
     </row>
+    <row r="2389">
+      <c r="A2389" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2389" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2389" t="n">
+        <v>0.044592</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2390" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2390" t="n">
+        <v>0.045911</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2391" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2391" t="n">
+        <v>0.04606</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2392" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2392" t="n">
+        <v>0.04598</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2393" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2393" t="n">
+        <v>0.046822</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2394" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2394" t="n">
+        <v>0.04833999999999999</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B2395" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2395" t="n">
+        <v>0.04754800000000001</v>
+      </c>
+    </row>
+    <row r="2396">
+      <c r="A2396" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2396" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2396" t="n">
+        <v>0.044105</v>
+      </c>
+    </row>
+    <row r="2397">
+      <c r="A2397" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2397" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2397" t="n">
+        <v>0.045138</v>
+      </c>
+    </row>
+    <row r="2398">
+      <c r="A2398" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2398" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2398" t="n">
+        <v>0.045279</v>
+      </c>
+    </row>
+    <row r="2399">
+      <c r="A2399" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2399" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2399" t="n">
+        <v>0.04525999999999999</v>
+      </c>
+    </row>
+    <row r="2400">
+      <c r="A2400" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2400" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2400" t="n">
+        <v>0.04622899999999999</v>
+      </c>
+    </row>
+    <row r="2401">
+      <c r="A2401" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2401" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2401" t="n">
+        <v>0.047899</v>
+      </c>
+    </row>
+    <row r="2402">
+      <c r="A2402" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2402" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2402" t="n">
+        <v>0.047188</v>
+      </c>
+    </row>
+    <row r="2403">
+      <c r="A2403" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2403" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C2403" t="n">
+        <v>0.04353100000000001</v>
+      </c>
+    </row>
+    <row r="2404">
+      <c r="A2404" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2404" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C2404" t="n">
+        <v>0.044363</v>
+      </c>
+    </row>
+    <row r="2405">
+      <c r="A2405" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2405" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C2405" t="n">
+        <v>0.044422</v>
+      </c>
+    </row>
+    <row r="2406">
+      <c r="A2406" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2406" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C2406" t="n">
+        <v>0.044456</v>
+      </c>
+    </row>
+    <row r="2407">
+      <c r="A2407" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2407" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C2407" t="n">
+        <v>0.04554299999999999</v>
+      </c>
+    </row>
+    <row r="2408">
+      <c r="A2408" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2408" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="C2408" t="n">
+        <v>0.047405</v>
+      </c>
+    </row>
+    <row r="2409">
+      <c r="A2409" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2409" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="C2409" t="n">
+        <v>0.04679000000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
